--- a/output/pdf_financials_xlsx/MOLY.xlsx
+++ b/output/pdf_financials_xlsx/MOLY.xlsx
@@ -1648,7 +1648,7 @@
         <v>2.09521</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>2.802436</v>
+        <v>5.942461</v>
       </c>
     </row>
     <row r="93">
@@ -2526,7 +2526,11 @@
           <t>WARRANT RESERVE (Note 5(c))</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MOLY.xlsx
+++ b/output/pdf_financials_xlsx/MOLY.xlsx
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.108582</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.17537</v>
       </c>
     </row>
     <row r="13">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-4.058773</v>
+        <v>-4.167355</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-7.514124</v>
+        <v>-7.689494</v>
       </c>
     </row>
     <row r="28">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-4.058773</v>
+        <v>-4.167355</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-7.514124</v>
+        <v>-7.689494</v>
       </c>
     </row>
     <row r="30">
@@ -3224,7 +3224,11 @@
           <t>General and administration expenses</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E37" s="5" t="n">
         <v>0.300563</v>
       </c>
@@ -3550,7 +3554,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
